--- a/output/pdf_financials_xlsx/ARCH.xlsx
+++ b/output/pdf_financials_xlsx/ARCH.xlsx
@@ -6781,7 +6781,7 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0.85803</v>
+        <v>0.8598479999999999</v>
       </c>
       <c r="C92" s="3" t="n">
         <v>0.85803</v>
@@ -18734,7 +18734,11 @@
           <t>Reserves (Note 14)</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E84" s="5" t="n">
         <v>0.001818</v>
       </c>

--- a/output/pdf_financials_xlsx/ARCH.xlsx
+++ b/output/pdf_financials_xlsx/ARCH.xlsx
@@ -1176,10 +1176,10 @@
         <v>0</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.01653</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.004072</v>
       </c>
       <c r="S12" s="3" t="n">
         <v>0</v>
@@ -2283,10 +2283,10 @@
         <v>-1.407857</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-3.326728</v>
+        <v>-3.343258</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-3.920288</v>
+        <v>-3.92436</v>
       </c>
       <c r="S27" s="3" t="n">
         <v>-1.552744</v>
@@ -2421,10 +2421,10 @@
         <v>-1.407857</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-3.326728</v>
+        <v>-3.343258</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-3.920288</v>
+        <v>-3.92436</v>
       </c>
       <c r="S29" s="3" t="n">
         <v>-1.552744</v>
@@ -2707,16 +2707,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.001874</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.029515</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.5062489999999999</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.205567</v>
       </c>
       <c r="F34" s="1" t="inlineStr">
         <is>
@@ -2724,16 +2724,16 @@
         </is>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.025594</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.365113</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.620822</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.199847</v>
       </c>
       <c r="K34" s="1" t="inlineStr">
         <is>
@@ -2741,16 +2741,16 @@
         </is>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.544324</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.400368</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.653685</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.448242</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>0.506348</v>
@@ -2841,16 +2841,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.001874</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.029515</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.5062489999999999</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.205567</v>
       </c>
       <c r="F36" s="1" t="inlineStr">
         <is>
@@ -2858,16 +2858,16 @@
         </is>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.025594</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.365113</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.620822</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.199847</v>
       </c>
       <c r="K36" s="1" t="inlineStr">
         <is>
@@ -2875,16 +2875,16 @@
         </is>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.544324</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.400368</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.653685</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.448242</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>0.506348</v>
@@ -3645,16 +3645,16 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.199775</v>
+        <v>0.197901</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.029515</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.51723</v>
+        <v>0.010981</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.21092</v>
+        <v>0.005353</v>
       </c>
       <c r="F48" s="1" t="inlineStr">
         <is>
@@ -3662,16 +3662,16 @@
         </is>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.036825</v>
+        <v>0.011231</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.405791</v>
+        <v>0.040678</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.649504</v>
+        <v>0.028682</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.227032</v>
+        <v>0.027185</v>
       </c>
       <c r="K48" s="1" t="inlineStr">
         <is>
@@ -3679,10 +3679,10 @@
         </is>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.85509</v>
+        <v>0.310766</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.567981</v>
+        <v>0.167613</v>
       </c>
       <c r="N48" s="3" t="n">
         <v>0</v>
@@ -13040,7 +13040,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E30" s="5" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -25548,7 +25548,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
